--- a/outputs/evaluation/decision/v2/CF_M05/run_2/CF_M05_decision_eval_gt_report.xlsx
+++ b/outputs/evaluation/decision/v2/CF_M05/run_2/CF_M05_decision_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,11 +509,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>This separation of responsibilities allows the client to focus on presentation and user experience, while the server focuses on business logic, security, data integrity, and persistence.</t>
+          <t>This microservice has the main function of routing all communications to the corresponding microservice within the system architecture.</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.6653</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="3">
@@ -552,194 +552,194 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>The use of this architecture allows high scalability, availability, and accessibility, as resource management can be done according to needs and anywhere with an Internet connection.</t>
+          <t>The portal microservice incorporates the binaries necessary for the frontEnd [...] of the rest of the applications of the portal. This ensures that the presentation layer is available and updated, facilitating deployment and reducing dependence on external elements.</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.6857</v>
+        <v>0.7473</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M05_AD04</t>
+          <t>CF_M05_AD07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>This microservice is essential for maintaining data confidentiality and protection.</t>
+          <t>This separation of responsibilities allows the client to focus on presentation and user experience.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>*CF_M05_C11</t>
+          <t>*CF_M05_C15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CF_M05_AU03</t>
+          <t>CF_M05_P02</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Confidentiality</t>
+          <t>Presentation and user experience</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Access Control Microservice</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_08</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>This separation of responsibilities allows the client to focus on presentation and user experience, while the server focuses on business logic, security, data integrity, and persistence.</t>
+          <t>The application follows the Client-Server pattern which organizes the code into two differentiated components: the client and the server. This separation of responsibilities allows the client to focus on presentation and user experience, while the server focuses on business logic, security, data integrity, and persistence.</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.6688</v>
+        <v>0.8127</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M05_AD05</t>
+          <t>CF_M05_AD09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>This component acts as a traceability and audit mechanism, ensuring that each interaction is documented for later analysis, incident resolution and regulatory compliance.</t>
+          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>*CF_M05_C13</t>
+          <t>CF_M05_C07, *CF_M05_C14, *CF_M05_C18</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CF_M05_AU04</t>
+          <t>CF_M05_AU30</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Traceability</t>
+          <t>Capacity; Maintainability; Scalability</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Communication Log Microservice</t>
+          <t>Angular</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>This separation of responsibilities allows the client to focus on presentation and user experience, while the server focuses on business logic, security, data integrity, and persistence.</t>
+          <t>This structure allows developing, deploying, and scaling each service autonomously, facilitating maintenance, flexibility, and the evolution of the system.</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.6309</v>
+        <v>0.7176</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M05_AD07</t>
+          <t>CF_M05_AD10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>This separation of responsibilities allows the client to focus on presentation and user experience.</t>
+          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>*CF_M05_C15</t>
+          <t>*CF_M05_C14</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CF_M05_P02</t>
+          <t>CF_M05_AU30, CF_M05_AU29</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Presentation and user experience</t>
+          <t>Maintainability</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>Angular; Spring Boot</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_09</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>This separation of responsibilities allows the client to focus on presentation and user experience, while the server focuses on business logic, security, data integrity, and persistence.</t>
+          <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services.</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.8676</v>
+        <v>0.6768999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M05_AD09</t>
+          <t>CF_M05_AD11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
+          <t>It allows you to automate the deployment, scaling and management of applications running in containers, run thousands of containers on different servers and ensure high availability.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CF_M05_C07, *CF_M05_C14, *CF_M05_C18</t>
+          <t>CF_M05_C06, CF_M05_C07</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CF_M05_AU30</t>
+          <t>CF_M05_AU07</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Capacity; Maintainability; Scalability</t>
+          <t>Availability; Capacity</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Angular</t>
+          <t>Amazon EKS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -753,18 +753,18 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.7176</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M05_AD10</t>
+          <t>CF_M05_AD12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
+          <t>This structure clarifies roles, avoids unnecessary coupling, and makes it easier to test, reuse, and maintain the code over time.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -774,11 +774,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CF_M05_AU30, CF_M05_AU29</t>
+          <t>CF_M05_AU29</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -787,37 +787,37 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Angular; Spring Boot</t>
+          <t>Spring Boot</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Angular applies the MVVM pattern, as its architecture is based on components and services.</t>
+          <t>This structure allows developing, deploying, and scaling each service autonomously, facilitating maintenance, flexibility, and the evolution of the system.</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.6804</v>
+        <v>0.7494</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M05_AD11</t>
+          <t>CF_M05_AD13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>It allows you to automate the deployment, scaling and management of applications running in containers, run thousands of containers on different servers and ensure high availability.</t>
+          <t>This diversity makes it easy to adapt to the needs of the project, allows the project to grow and scale in an agile manner and eliminates the need to look for other platforms when requirements evolve.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CF_M05_C06, CF_M05_C07</t>
+          <t>*CF_M05_C18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -826,11 +826,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Availability; Capacity</t>
+          <t>Scalability</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -840,64 +840,16 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>The use of this architecture allows high scalability, availability, and accessibility, as resource management can be done according to needs and anywhere with an Internet connection.</t>
+          <t>This structure allows developing, deploying, and scaling each service autonomously, facilitating maintenance, flexibility, and the evolution of the system.</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0.7877999999999999</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CF_M05_AD12</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>This structure clarifies roles, avoids unnecessary coupling, and makes it easier to test, reuse, and maintain the code over time.</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>*CF_M05_C14</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CF_M05_AU29</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>78</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Maintainability</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Spring Boot</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>AD_01</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>This structure allows developing, deploying, and scaling each service autonomously, facilitating maintenance, flexibility, and the evolution of the system.</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>0.7494</v>
+        <v>0.767</v>
       </c>
     </row>
   </sheetData>
